--- a/experiments/E2_model_size_resolution/results/results.xlsx
+++ b/experiments/E2_model_size_resolution/results/results.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>yolo26n_960</t>
+          <t>yolo26s_640</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="19" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="19" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
@@ -672,55 +672,55 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>yolo26n_960</t>
+          <t>yolo26s_640</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yolo26n</t>
+          <t>yolo26s</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>960</v>
+        <v>640</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5482366842212372</v>
+        <v>0.5582442635929081</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2980879105238469</v>
+        <v>0.3098031105961577</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6133749902657546</v>
+        <v>0.608780406953327</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5003300086367306</v>
+        <v>0.5227505506483571</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4608811153606738</v>
+        <v>0.4670764654953006</v>
       </c>
       <c r="I2" t="n">
-        <v>0.479642613745527</v>
+        <v>0.4949631259147543</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5796095012091134</v>
+        <v>0.5760896650312759</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6728135065696347</v>
+        <v>0.6948477979303016</v>
       </c>
       <c r="L2" t="n">
-        <v>2.535344</v>
+        <v>9.95096</v>
       </c>
       <c r="M2" t="n">
-        <v>5.515525</v>
+        <v>20.311877</v>
       </c>
       <c r="N2" t="n">
-        <v>268.0031957998532</v>
+        <v>317.2873389665862</v>
       </c>
       <c r="O2" t="n">
-        <v>254.93355473324</v>
+        <v>310.5194087333075</v>
       </c>
       <c r="P2" t="n">
-        <v>2.045634876050749</v>
+        <v>1.759428111474997</v>
       </c>
     </row>
   </sheetData>

--- a/experiments/E2_model_size_resolution/results/results.xlsx
+++ b/experiments/E2_model_size_resolution/results/results.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>yolo26s_640</t>
+          <t>yolo26s_960</t>
         </is>
       </c>
     </row>
@@ -578,11 +578,11 @@
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
@@ -672,7 +672,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>yolo26s_640</t>
+          <t>yolo26s_960</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -681,46 +681,46 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>640</v>
+        <v>960</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5582442635929081</v>
+        <v>0.5626824148871852</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3098031105961577</v>
+        <v>0.3033567481546558</v>
       </c>
       <c r="F2" t="n">
-        <v>0.608780406953327</v>
+        <v>0.6098403670190369</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5227505506483571</v>
+        <v>0.527930140585815</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4670764654953006</v>
+        <v>0.5006101652887758</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4949631259147543</v>
+        <v>0.4950695730393903</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5760896650312759</v>
+        <v>0.5742074090570968</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6948477979303016</v>
+        <v>0.6808425121634778</v>
       </c>
       <c r="L2" t="n">
         <v>9.95096</v>
       </c>
       <c r="M2" t="n">
-        <v>20.311877</v>
+        <v>20.377413</v>
       </c>
       <c r="N2" t="n">
-        <v>317.2873389665862</v>
+        <v>755.5100900327185</v>
       </c>
       <c r="O2" t="n">
-        <v>310.5194087333075</v>
+        <v>743.7606658330575</v>
       </c>
       <c r="P2" t="n">
-        <v>1.759428111474997</v>
+        <v>0.7447715421812796</v>
       </c>
     </row>
   </sheetData>

--- a/experiments/E2_model_size_resolution/results/results.xlsx
+++ b/experiments/E2_model_size_resolution/results/results.xlsx
@@ -430,7 +430,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="49" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>yolo26s_960</t>
+          <t>yolo26n_640,yolo26n_960,yolo26s_640,yolo26s_960</t>
         </is>
       </c>
     </row>
@@ -571,24 +571,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
-    <col width="19" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
@@ -672,55 +672,217 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
+          <t>yolo26n_640</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>yolo26n</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>640</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5258994427030856</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.2916875624122405</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.6002285393908908</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.4932542698847047</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.4371800022388831</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.464273885130185</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.5415180395226973</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.6606258439205772</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.535344</v>
+      </c>
+      <c r="M2" t="n">
+        <v>5.449989</v>
+      </c>
+      <c r="N2" t="n">
+        <v>101.4151038997321</v>
+      </c>
+      <c r="O2" t="n">
+        <v>96.1432767999213</v>
+      </c>
+      <c r="P2" t="n">
+        <v>5.18561262061158</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>yolo26n_960</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>yolo26n</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>960</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5482366842212372</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.2980879105238469</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6133749902657546</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5003300086367306</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.4608811153606738</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.479642613745527</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5796095012091134</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.6728135065696347</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.535344</v>
+      </c>
+      <c r="M3" t="n">
+        <v>5.515525</v>
+      </c>
+      <c r="N3" t="n">
+        <v>231.3781191661595</v>
+      </c>
+      <c r="O3" t="n">
+        <v>220.5081572661584</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.369440490729947</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>yolo26s_640</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>yolo26s</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>640</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.5582442635929081</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.3098031105961577</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.608780406953327</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5227505506483571</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.4670764654953006</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.4949631259147543</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.5760896650312759</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.6948477979303016</v>
+      </c>
+      <c r="L4" t="n">
+        <v>9.95096</v>
+      </c>
+      <c r="M4" t="n">
+        <v>20.311877</v>
+      </c>
+      <c r="N4" t="n">
+        <v>304.8435447664814</v>
+      </c>
+      <c r="O4" t="n">
+        <v>298.7733586663429</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.831248432767499</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
           <t>yolo26s_960</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>yolo26s</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C5" t="n">
         <v>960</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D5" t="n">
         <v>0.5626824148871852</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E5" t="n">
         <v>0.3033567481546558</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F5" t="n">
         <v>0.6098403670190369</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G5" t="n">
         <v>0.527930140585815</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H5" t="n">
         <v>0.5006101652887758</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I5" t="n">
         <v>0.4950695730393903</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J5" t="n">
         <v>0.5742074090570968</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K5" t="n">
         <v>0.6808425121634778</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L5" t="n">
         <v>9.95096</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M5" t="n">
         <v>20.377413</v>
       </c>
-      <c r="N2" t="n">
-        <v>755.5100900327185</v>
-      </c>
-      <c r="O2" t="n">
-        <v>743.7606658330575</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.7447715421812796</v>
+      <c r="N5" t="n">
+        <v>702.5787688669274</v>
+      </c>
+      <c r="O5" t="n">
+        <v>690.746524032996</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.8008816090395703</v>
       </c>
     </row>
   </sheetData>
